--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\Ejemplos_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1139DB94-FC4F-4226-B760-1E9216CD6114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007A9A2E-A25B-416D-84C4-40B44BE64870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6615" yWindow="2010" windowWidth="16680" windowHeight="10290" firstSheet="3" activeTab="5" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="6" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Frecuencias_Ej1" sheetId="3" r:id="rId3"/>
     <sheet name="Intervalos_Ej2" sheetId="4" r:id="rId4"/>
     <sheet name="Intervalos_Ej2.5" sheetId="5" r:id="rId5"/>
-    <sheet name="Ejemplo 2.9" sheetId="6" r:id="rId6"/>
+    <sheet name="Ejemplo 2.9 (Bivariante)" sheetId="6" r:id="rId6"/>
+    <sheet name="Ejemplo 4.10 (Pearson)" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="136">
   <si>
     <t>Datos 1</t>
   </si>
@@ -258,14 +259,211 @@
   </si>
   <si>
     <t>Moneda</t>
+  </si>
+  <si>
+    <t>Entidades</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>NACIONAL DE BOLIVIA</t>
+  </si>
+  <si>
+    <t>MERCANTIL SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>CREDITO DE BOLIVIA</t>
+  </si>
+  <si>
+    <t>UNIÓN</t>
+  </si>
+  <si>
+    <t>ECONÓMICO</t>
+  </si>
+  <si>
+    <t>GANADERO</t>
+  </si>
+  <si>
+    <t>BANCO SOLIDARIO</t>
+  </si>
+  <si>
+    <t>BANCO PYME LOS ANDES</t>
+  </si>
+  <si>
+    <t>BANCO FIE</t>
+  </si>
+  <si>
+    <t>BANCO FORTALEZA</t>
+  </si>
+  <si>
+    <t>BANCO FASSIL</t>
+  </si>
+  <si>
+    <t>BANCO PYME DE LA COMUNIDAD</t>
+  </si>
+  <si>
+    <t>BANCO PYME ECO FUTURO</t>
+  </si>
+  <si>
+    <t>BANCO PRODEM</t>
+  </si>
+  <si>
+    <t>Σ</t>
+  </si>
+  <si>
+    <t>(xᵢ − μx)^22</t>
+  </si>
+  <si>
+    <t>(yᵢ − μy)^22</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>14.76</t>
+  </si>
+  <si>
+    <t>0.152881</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>13.87</t>
+  </si>
+  <si>
+    <t>0.919681</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>16.56</t>
+  </si>
+  <si>
+    <t>0.474721</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>17.03</t>
+  </si>
+  <si>
+    <t>0.591361</t>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>20.15</t>
+  </si>
+  <si>
+    <t>1.55</t>
+  </si>
+  <si>
+    <t>9.31</t>
+  </si>
+  <si>
+    <t>0.337561</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>23.50</t>
+  </si>
+  <si>
+    <t>0.758641</t>
+  </si>
+  <si>
+    <t>1.88</t>
+  </si>
+  <si>
+    <t>5.74</t>
+  </si>
+  <si>
+    <t>0.829921</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>25.01</t>
+  </si>
+  <si>
+    <t>0.436921</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>22.56</t>
+  </si>
+  <si>
+    <t>0.108241</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>19.66</t>
+  </si>
+  <si>
+    <t>0.358801</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>25.51</t>
+  </si>
+  <si>
+    <t>0.323761</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>27.45</t>
+  </si>
+  <si>
+    <t>0.312481</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>19.72</t>
+  </si>
+  <si>
+    <t>0.009801</t>
+  </si>
+  <si>
+    <t>13.57</t>
+  </si>
+  <si>
+    <t>260.83</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -293,12 +491,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1911,4 +2124,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA88322-07D3-4CA5-80F8-5FC9666E282A}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="6">
+        <v>14984641</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="6">
+        <v>22667121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="6">
+        <v>4289041</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2563201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1347921</v>
+      </c>
+      <c r="E6" s="6">
+        <v>2307361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="6">
+        <v>86881041</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="6">
+        <v>23707161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="6">
+        <v>166177881</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="6">
+        <v>40691641</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="6">
+        <v>15437041</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1058841</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="6">
+        <v>47320641</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="6">
+        <v>7774761</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1185921</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="7">
+        <v>6962694</v>
+      </c>
+      <c r="E16" s="7">
+        <v>507046294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007A9A2E-A25B-416D-84C4-40B44BE64870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F2A77-BD02-49E7-A294-176B358D581A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="6" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="1620" yWindow="1590" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="7" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Intervalos_Ej2.5" sheetId="5" r:id="rId5"/>
     <sheet name="Ejemplo 2.9 (Bivariante)" sheetId="6" r:id="rId6"/>
     <sheet name="Ejemplo 4.10 (Pearson)" sheetId="7" r:id="rId7"/>
+    <sheet name="Ejemplo 3.57 (Box-Plot)" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="137">
   <si>
     <t>Datos 1</t>
   </si>
@@ -448,13 +449,16 @@
   </si>
   <si>
     <t>260.83</t>
+  </si>
+  <si>
+    <t>40 ejecutivos de marketing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +470,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2411,4 +2421,223 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DA3CF2-E51D-480C-92D7-6F2DE36953E8}">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F2A77-BD02-49E7-A294-176B358D581A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91487FC-AFAA-4F5C-BC87-CD0A7381EDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1620" yWindow="1590" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="7" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Ejemplo 2.9 (Bivariante)" sheetId="6" r:id="rId6"/>
     <sheet name="Ejemplo 4.10 (Pearson)" sheetId="7" r:id="rId7"/>
     <sheet name="Ejemplo 3.57 (Box-Plot)" sheetId="8" r:id="rId8"/>
+    <sheet name="Ejemplo 5.1" sheetId="9" r:id="rId9"/>
+    <sheet name="Ejemplo 5.6" sheetId="10" r:id="rId10"/>
+    <sheet name="Hoja3" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="148">
   <si>
     <t>Datos 1</t>
   </si>
@@ -452,6 +455,39 @@
   </si>
   <si>
     <t>40 ejecutivos de marketing</t>
+  </si>
+  <si>
+    <t>Periodo</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>21.6</t>
+  </si>
+  <si>
+    <t>37.6</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Total ventas (Y)</t>
+  </si>
+  <si>
+    <t>Publicidad (X)</t>
+  </si>
+  <si>
+    <t>Gastos en alimentacion</t>
+  </si>
+  <si>
+    <t>Ingreso</t>
+  </si>
+  <si>
+    <t>Horas</t>
+  </si>
+  <si>
+    <t>Satisfacción en el trabajo</t>
   </si>
 </sst>
 </file>
@@ -501,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -521,6 +557,18 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -900,6 +948,481 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C53ABA-7916-4CB1-8FED-A33FDB0CD5F9}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" style="8" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B3" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3000</v>
+      </c>
+      <c r="B4" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B5" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>6000</v>
+      </c>
+      <c r="B6" s="8">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B7" s="8">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B8" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B9" s="8">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>1580</v>
+      </c>
+      <c r="B10" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B11" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B12" s="8">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>4000</v>
+      </c>
+      <c r="B13" s="8">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>5600</v>
+      </c>
+      <c r="B14" s="8">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>5300</v>
+      </c>
+      <c r="B15" s="8">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>4600</v>
+      </c>
+      <c r="B16" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B17" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>3500</v>
+      </c>
+      <c r="B18" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>2800</v>
+      </c>
+      <c r="B19" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>3020</v>
+      </c>
+      <c r="B20" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B21" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>5600</v>
+      </c>
+      <c r="B22" s="8">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>8000</v>
+      </c>
+      <c r="B23" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="8">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B25" s="8">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B26" s="8">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>6000</v>
+      </c>
+      <c r="B27" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>5300</v>
+      </c>
+      <c r="B28" s="8">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B29" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>2300</v>
+      </c>
+      <c r="B30" s="8">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>2800</v>
+      </c>
+      <c r="B31" s="8">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B32" s="8">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>2000</v>
+      </c>
+      <c r="B33" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B34" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B35" s="8">
+        <v>17000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066FAF81-566D-484C-83F8-1E7D9A3EBB16}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>70</v>
+      </c>
+      <c r="B2" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>80</v>
+      </c>
+      <c r="B3" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>80</v>
+      </c>
+      <c r="B4" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>70</v>
+      </c>
+      <c r="B5" s="11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>85</v>
+      </c>
+      <c r="B6" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>70</v>
+      </c>
+      <c r="B7" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>35</v>
+      </c>
+      <c r="B8" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>90</v>
+      </c>
+      <c r="B9" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>85</v>
+      </c>
+      <c r="B10" s="11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>65</v>
+      </c>
+      <c r="B11" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>85</v>
+      </c>
+      <c r="B12" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>75</v>
+      </c>
+      <c r="B13" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>75</v>
+      </c>
+      <c r="B14" s="11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>80</v>
+      </c>
+      <c r="B15" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>50</v>
+      </c>
+      <c r="B16" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>70</v>
+      </c>
+      <c r="B17" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>80</v>
+      </c>
+      <c r="B18" s="11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>60</v>
+      </c>
+      <c r="B19" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>65</v>
+      </c>
+      <c r="B20" s="11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>30</v>
+      </c>
+      <c r="B21" s="11">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5286FA33-8335-4F16-8FFE-4911A034FBC6}">
   <dimension ref="A1:B7"/>
@@ -2640,4 +3163,141 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8381F06-0351-45EA-8205-A1AB884EB138}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="11.42578125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
+        <v>150</v>
+      </c>
+      <c r="C2" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
+        <v>75</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8">
+        <v>338</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8">
+        <v>750</v>
+      </c>
+      <c r="C5" s="8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8">
+        <v>541</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8">
+        <v>89</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8">
+        <v>126</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8">
+        <v>379</v>
+      </c>
+      <c r="C9" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8">
+        <v>650</v>
+      </c>
+      <c r="C10" s="8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8">
+        <v>350</v>
+      </c>
+      <c r="C11" s="8">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91487FC-AFAA-4F5C-BC87-CD0A7381EDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B8F9FA-13B2-4DA8-9C68-4BB9DCDB3322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="10" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="12225" yWindow="1755" windowWidth="14730" windowHeight="11295" firstSheet="9" activeTab="10" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
     <sheet name="Datos2_Ej1" sheetId="1" r:id="rId2"/>
     <sheet name="Frecuencias_Ej1" sheetId="3" r:id="rId3"/>
-    <sheet name="Intervalos_Ej2" sheetId="4" r:id="rId4"/>
-    <sheet name="Intervalos_Ej2.5" sheetId="5" r:id="rId5"/>
-    <sheet name="Ejemplo 2.9 (Bivariante)" sheetId="6" r:id="rId6"/>
-    <sheet name="Ejemplo 4.10 (Pearson)" sheetId="7" r:id="rId7"/>
-    <sheet name="Ejemplo 3.57 (Box-Plot)" sheetId="8" r:id="rId8"/>
-    <sheet name="Ejemplo 5.1" sheetId="9" r:id="rId9"/>
-    <sheet name="Ejemplo 5.6" sheetId="10" r:id="rId10"/>
-    <sheet name="Hoja3" sheetId="11" r:id="rId11"/>
+    <sheet name="Intervalos_Ej2.5" sheetId="5" r:id="rId4"/>
+    <sheet name="Ejemplo 2.9 (Bivariante)" sheetId="6" r:id="rId5"/>
+    <sheet name="Ejemplo 4.10 (Pearson)" sheetId="7" r:id="rId6"/>
+    <sheet name="Ejemplo 3.57 (Box-Plot)" sheetId="8" r:id="rId7"/>
+    <sheet name="Ejemplo 5.1 (Regresion)" sheetId="9" r:id="rId8"/>
+    <sheet name="Ejemplo 5.6 (Regresion)" sheetId="10" r:id="rId9"/>
+    <sheet name="Ejemplo 5.8 (Regresion)" sheetId="11" r:id="rId10"/>
+    <sheet name="Ejemplo 6.1 (N.Indices)" sheetId="14" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="156">
   <si>
     <t>Datos 1</t>
   </si>
@@ -64,24 +64,6 @@
     <t>Cant. Piezas defectuosas</t>
   </si>
   <si>
-    <t>LI - LS</t>
-  </si>
-  <si>
-    <t>f_i</t>
-  </si>
-  <si>
-    <t>10 , 19</t>
-  </si>
-  <si>
-    <t>20 , 29</t>
-  </si>
-  <si>
-    <t>30 , 39</t>
-  </si>
-  <si>
-    <t>40 , 49</t>
-  </si>
-  <si>
     <t>Planilla de sueldos y salarios de la institucion ABC</t>
   </si>
   <si>
@@ -488,6 +470,48 @@
   </si>
   <si>
     <t>Satisfacción en el trabajo</t>
+  </si>
+  <si>
+    <t>96.22</t>
+  </si>
+  <si>
+    <t>105.99</t>
+  </si>
+  <si>
+    <t>121.82</t>
+  </si>
+  <si>
+    <t>152.16</t>
+  </si>
+  <si>
+    <t>198.16</t>
+  </si>
+  <si>
+    <t>241.30</t>
+  </si>
+  <si>
+    <t>257.75</t>
+  </si>
+  <si>
+    <t>306.71</t>
+  </si>
+  <si>
+    <t>367.52</t>
+  </si>
+  <si>
+    <t>426.20</t>
+  </si>
+  <si>
+    <t>502.02</t>
+  </si>
+  <si>
+    <t>Índice base = 2003</t>
+  </si>
+  <si>
+    <t>Depósitos del publico (Millones USD)</t>
+  </si>
+  <si>
+    <t>Año (Dic)</t>
   </si>
 </sst>
 </file>
@@ -537,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -569,6 +593,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -949,300 +976,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C53ABA-7916-4CB1-8FED-A33FDB0CD5F9}">
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.28515625" style="8" customWidth="1"/>
-    <col min="2" max="16384" width="11.42578125" style="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>1500</v>
-      </c>
-      <c r="B3" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>3000</v>
-      </c>
-      <c r="B4" s="8">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>4500</v>
-      </c>
-      <c r="B5" s="8">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>6000</v>
-      </c>
-      <c r="B6" s="8">
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>6500</v>
-      </c>
-      <c r="B7" s="8">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>1500</v>
-      </c>
-      <c r="B8" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>1500</v>
-      </c>
-      <c r="B9" s="8">
-        <v>5550</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>1580</v>
-      </c>
-      <c r="B10" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>2500</v>
-      </c>
-      <c r="B11" s="8">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <v>2500</v>
-      </c>
-      <c r="B12" s="8">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>4000</v>
-      </c>
-      <c r="B13" s="8">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <v>5600</v>
-      </c>
-      <c r="B14" s="8">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>5300</v>
-      </c>
-      <c r="B15" s="8">
-        <v>8500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>4600</v>
-      </c>
-      <c r="B16" s="8">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <v>4500</v>
-      </c>
-      <c r="B17" s="8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <v>3500</v>
-      </c>
-      <c r="B18" s="8">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
-        <v>2800</v>
-      </c>
-      <c r="B19" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
-        <v>3020</v>
-      </c>
-      <c r="B20" s="8">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <v>2500</v>
-      </c>
-      <c r="B21" s="8">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <v>5600</v>
-      </c>
-      <c r="B22" s="8">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
-        <v>8000</v>
-      </c>
-      <c r="B23" s="8">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
-        <v>10000</v>
-      </c>
-      <c r="B24" s="8">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <v>6500</v>
-      </c>
-      <c r="B25" s="8">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
-        <v>4500</v>
-      </c>
-      <c r="B26" s="8">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>6000</v>
-      </c>
-      <c r="B27" s="8">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
-        <v>5300</v>
-      </c>
-      <c r="B28" s="8">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
-        <v>7500</v>
-      </c>
-      <c r="B29" s="8">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <v>2300</v>
-      </c>
-      <c r="B30" s="8">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
-        <v>2800</v>
-      </c>
-      <c r="B31" s="8">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <v>7500</v>
-      </c>
-      <c r="B32" s="8">
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <v>2000</v>
-      </c>
-      <c r="B33" s="8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
-        <v>6500</v>
-      </c>
-      <c r="B34" s="8">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
-        <v>6500</v>
-      </c>
-      <c r="B35" s="8">
-        <v>17000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066FAF81-566D-484C-83F8-1E7D9A3EBB16}">
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1252,10 +985,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1419,6 +1152,178 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1805438-2CDA-4D32-B74F-41E3096D7714}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>3</v>
+      </c>
+      <c r="B2" s="10">
+        <v>3470</v>
+      </c>
+      <c r="C2" s="10">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10">
+        <v>3339</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10">
+        <v>3678</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>6</v>
+      </c>
+      <c r="B5" s="10">
+        <v>4227</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>7</v>
+      </c>
+      <c r="B6" s="10">
+        <v>5280</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10">
+        <v>6876</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>9</v>
+      </c>
+      <c r="B8" s="10">
+        <v>8373</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>10</v>
+      </c>
+      <c r="B9" s="10">
+        <v>8944</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10">
+        <v>10643</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>12</v>
+      </c>
+      <c r="B11" s="10">
+        <v>12753</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>13</v>
+      </c>
+      <c r="B12" s="10">
+        <v>14789</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>14</v>
+      </c>
+      <c r="B13" s="10">
+        <v>17420</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1752,48 +1657,263 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDBDFC2D-AD15-45F4-8544-9662D8A5E844}">
-  <dimension ref="A1:B5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5001DBD-AAC3-41E2-9650-E87669B5D519}">
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>7290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>5790</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>8350</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>8450</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>8440</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>8460</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>15490</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>8550</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>8870</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>12650</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>8500</v>
       </c>
     </row>
   </sheetData>
@@ -1802,263 +1922,591 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5001DBD-AAC3-41E2-9650-E87669B5D519}">
-  <dimension ref="A1:A51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EEB6C63-34E1-4EB8-A5AB-FD3CF2C483CB}">
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>6900</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>6700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>7290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>7300</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>7400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>7450</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>11700</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>7700</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>7900</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>8100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>9500</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>10200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>5790</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>8220</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>8350</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>8450</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>8440</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>8460</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>15490</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>8550</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>8870</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>8880</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>12400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>12600</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>12650</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>8500</v>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2067,599 +2515,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EEB6C63-34E1-4EB8-A5AB-FD3CF2C483CB}">
-  <dimension ref="A1:C53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" t="s">
-        <v>14</v>
-      </c>
-      <c r="C41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>58</v>
-      </c>
-      <c r="B42" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>14</v>
-      </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" t="s">
-        <v>14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>67</v>
-      </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-      <c r="B52" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEA88322-07D3-4CA5-80F8-5FC9666E282A}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2671,33 +2526,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E2" s="6">
         <v>14984641</v>
@@ -2705,16 +2560,16 @@
     </row>
     <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E3" s="6">
         <v>22667121</v>
@@ -2722,16 +2577,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6">
         <v>4289041</v>
@@ -2739,16 +2594,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E5" s="6">
         <v>2563201</v>
@@ -2756,13 +2611,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6">
         <v>1347921</v>
@@ -2773,16 +2628,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E7" s="6">
         <v>86881041</v>
@@ -2790,16 +2645,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E8" s="6">
         <v>23707161</v>
@@ -2807,16 +2662,16 @@
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E9" s="6">
         <v>166177881</v>
@@ -2824,16 +2679,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E10" s="6">
         <v>40691641</v>
@@ -2841,16 +2696,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E11" s="6">
         <v>15437041</v>
@@ -2858,16 +2713,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E12" s="6">
         <v>1058841</v>
@@ -2875,16 +2730,16 @@
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E13" s="6">
         <v>47320641</v>
@@ -2892,16 +2747,16 @@
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E14" s="6">
         <v>7774761</v>
@@ -2909,16 +2764,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E15" s="6">
         <v>1185921</v>
@@ -2926,13 +2781,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D16" s="7">
         <v>6962694</v>
@@ -2946,7 +2801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DA3CF2-E51D-480C-92D7-6F2DE36953E8}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2956,7 +2811,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -3165,7 +3020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8381F06-0351-45EA-8205-A1AB884EB138}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3178,13 +3033,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -3206,7 +3061,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3217,7 +3072,7 @@
         <v>338</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3239,7 +3094,7 @@
         <v>541</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3250,7 +3105,7 @@
         <v>89</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,6 +3150,300 @@
       </c>
       <c r="C11" s="8">
         <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C53ABA-7916-4CB1-8FED-A33FDB0CD5F9}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" style="8" customWidth="1"/>
+    <col min="2" max="16384" width="11.42578125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B3" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3000</v>
+      </c>
+      <c r="B4" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B5" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>6000</v>
+      </c>
+      <c r="B6" s="8">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B7" s="8">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B8" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>1500</v>
+      </c>
+      <c r="B9" s="8">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>1580</v>
+      </c>
+      <c r="B10" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B11" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B12" s="8">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>4000</v>
+      </c>
+      <c r="B13" s="8">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>5600</v>
+      </c>
+      <c r="B14" s="8">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>5300</v>
+      </c>
+      <c r="B15" s="8">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>4600</v>
+      </c>
+      <c r="B16" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B17" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>3500</v>
+      </c>
+      <c r="B18" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>2800</v>
+      </c>
+      <c r="B19" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>3020</v>
+      </c>
+      <c r="B20" s="8">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>2500</v>
+      </c>
+      <c r="B21" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>5600</v>
+      </c>
+      <c r="B22" s="8">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>8000</v>
+      </c>
+      <c r="B23" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>10000</v>
+      </c>
+      <c r="B24" s="8">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B25" s="8">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>4500</v>
+      </c>
+      <c r="B26" s="8">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>6000</v>
+      </c>
+      <c r="B27" s="8">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>5300</v>
+      </c>
+      <c r="B28" s="8">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B29" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
+        <v>2300</v>
+      </c>
+      <c r="B30" s="8">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>2800</v>
+      </c>
+      <c r="B31" s="8">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>7500</v>
+      </c>
+      <c r="B32" s="8">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>2000</v>
+      </c>
+      <c r="B33" s="8">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B34" s="8">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>6500</v>
+      </c>
+      <c r="B35" s="8">
+        <v>17000</v>
       </c>
     </row>
   </sheetData>

--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B8F9FA-13B2-4DA8-9C68-4BB9DCDB3322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC398FAD-0C45-4E61-B2E5-B693ABD3FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12225" yWindow="1755" windowWidth="14730" windowHeight="11295" firstSheet="9" activeTab="10" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="11130" yWindow="2370" windowWidth="14730" windowHeight="11295" firstSheet="11" activeTab="13" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="Ejemplo 5.6 (Regresion)" sheetId="10" r:id="rId9"/>
     <sheet name="Ejemplo 5.8 (Regresion)" sheetId="11" r:id="rId10"/>
     <sheet name="Ejemplo 6.1 (N.Indices)" sheetId="14" r:id="rId11"/>
+    <sheet name="Ejemplo 6.2 (N.Indices)" sheetId="15" r:id="rId12"/>
+    <sheet name="Ejemplo 5.7 (Regresion Cuad.)" sheetId="16" r:id="rId13"/>
+    <sheet name="Ejemplo 6.9 (N. Indice)" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="177">
   <si>
     <t>Datos 1</t>
   </si>
@@ -512,6 +515,69 @@
   </si>
   <si>
     <t>Año (Dic)</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Directivos</t>
+  </si>
+  <si>
+    <t>Profesionales</t>
+  </si>
+  <si>
+    <t>Administrativos</t>
+  </si>
+  <si>
+    <t>Personal de servicio</t>
+  </si>
+  <si>
+    <t>Obreros</t>
+  </si>
+  <si>
+    <t>Eventuales</t>
+  </si>
+  <si>
+    <t>Tasa Bonos (Y)</t>
+  </si>
+  <si>
+    <t>Tasa Prestamos (X)</t>
+  </si>
+  <si>
+    <t>Artículo</t>
+  </si>
+  <si>
+    <t>Leche (Lt)</t>
+  </si>
+  <si>
+    <t>Carne de Res (Kg)</t>
+  </si>
+  <si>
+    <t>Arroz (Lb)</t>
+  </si>
+  <si>
+    <t>Papa (@)</t>
+  </si>
+  <si>
+    <t>Precio (2013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cantidad (2013)</t>
+  </si>
+  <si>
+    <t>Precio (2014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cantidad (2014 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cantidad (2015)</t>
+  </si>
+  <si>
+    <t>Precio (2015)</t>
   </si>
 </sst>
 </file>
@@ -561,7 +627,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -593,9 +659,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1174,7 +1237,7 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>3</v>
       </c>
       <c r="B2" s="10">
@@ -1186,7 +1249,7 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>4</v>
       </c>
       <c r="B3" s="10">
@@ -1198,7 +1261,7 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>5</v>
       </c>
       <c r="B4" s="10">
@@ -1210,7 +1273,7 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>6</v>
       </c>
       <c r="B5" s="10">
@@ -1222,7 +1285,7 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>7</v>
       </c>
       <c r="B6" s="10">
@@ -1234,7 +1297,7 @@
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>8</v>
       </c>
       <c r="B7" s="10">
@@ -1246,7 +1309,7 @@
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>9</v>
       </c>
       <c r="B8" s="10">
@@ -1258,7 +1321,7 @@
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>10</v>
       </c>
       <c r="B9" s="10">
@@ -1270,7 +1333,7 @@
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>11</v>
       </c>
       <c r="B10" s="10">
@@ -1282,7 +1345,7 @@
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>12</v>
       </c>
       <c r="B11" s="10">
@@ -1294,7 +1357,7 @@
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>13</v>
       </c>
       <c r="B12" s="10">
@@ -1306,7 +1369,7 @@
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>14</v>
       </c>
       <c r="B13" s="10">
@@ -1324,6 +1387,552 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C35F1F3-544E-4D86-AB08-05B8A66C403F}">
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="10">
+        <v>2004</v>
+      </c>
+      <c r="C1" s="10">
+        <v>2005</v>
+      </c>
+      <c r="D1" s="10">
+        <v>2006</v>
+      </c>
+      <c r="E1" s="10">
+        <v>2007</v>
+      </c>
+      <c r="F1" s="10">
+        <v>2008</v>
+      </c>
+      <c r="G1" s="10">
+        <v>2009</v>
+      </c>
+      <c r="H1" s="10">
+        <v>2010</v>
+      </c>
+      <c r="I1" s="10">
+        <v>2011</v>
+      </c>
+      <c r="J1" s="10">
+        <v>2012</v>
+      </c>
+      <c r="K1" s="10">
+        <v>2013</v>
+      </c>
+      <c r="L1" s="10">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="10">
+        <v>164</v>
+      </c>
+      <c r="C2" s="10">
+        <v>163</v>
+      </c>
+      <c r="D2" s="10">
+        <v>161</v>
+      </c>
+      <c r="E2" s="10">
+        <v>166</v>
+      </c>
+      <c r="F2" s="10">
+        <v>173</v>
+      </c>
+      <c r="G2" s="10">
+        <v>184</v>
+      </c>
+      <c r="H2" s="10">
+        <v>191</v>
+      </c>
+      <c r="I2" s="10">
+        <v>200</v>
+      </c>
+      <c r="J2" s="10">
+        <v>217</v>
+      </c>
+      <c r="K2" s="10">
+        <v>235</v>
+      </c>
+      <c r="L2" s="10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="10">
+        <v>152</v>
+      </c>
+      <c r="C3" s="10">
+        <v>151</v>
+      </c>
+      <c r="D3" s="10">
+        <v>144</v>
+      </c>
+      <c r="E3" s="10">
+        <v>147</v>
+      </c>
+      <c r="F3" s="10">
+        <v>152</v>
+      </c>
+      <c r="G3" s="10">
+        <v>157</v>
+      </c>
+      <c r="H3" s="10">
+        <v>159</v>
+      </c>
+      <c r="I3" s="10">
+        <v>155</v>
+      </c>
+      <c r="J3" s="10">
+        <v>155</v>
+      </c>
+      <c r="K3" s="10">
+        <v>174</v>
+      </c>
+      <c r="L3" s="10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="10">
+        <v>178</v>
+      </c>
+      <c r="C4" s="10">
+        <v>176</v>
+      </c>
+      <c r="D4" s="10">
+        <v>175</v>
+      </c>
+      <c r="E4" s="10">
+        <v>181</v>
+      </c>
+      <c r="F4" s="10">
+        <v>185</v>
+      </c>
+      <c r="G4" s="10">
+        <v>196</v>
+      </c>
+      <c r="H4" s="10">
+        <v>201</v>
+      </c>
+      <c r="I4" s="10">
+        <v>211</v>
+      </c>
+      <c r="J4" s="10">
+        <v>230</v>
+      </c>
+      <c r="K4" s="10">
+        <v>250</v>
+      </c>
+      <c r="L4" s="10">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="10">
+        <v>156</v>
+      </c>
+      <c r="C5" s="10">
+        <v>156</v>
+      </c>
+      <c r="D5" s="10">
+        <v>154</v>
+      </c>
+      <c r="E5" s="10">
+        <v>159</v>
+      </c>
+      <c r="F5" s="10">
+        <v>164</v>
+      </c>
+      <c r="G5" s="10">
+        <v>179</v>
+      </c>
+      <c r="H5" s="10">
+        <v>180</v>
+      </c>
+      <c r="I5" s="10">
+        <v>192</v>
+      </c>
+      <c r="J5" s="10">
+        <v>208</v>
+      </c>
+      <c r="K5" s="10">
+        <v>220</v>
+      </c>
+      <c r="L5" s="10">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="10">
+        <v>154</v>
+      </c>
+      <c r="C6" s="10">
+        <v>154</v>
+      </c>
+      <c r="D6" s="10">
+        <v>151</v>
+      </c>
+      <c r="E6" s="10">
+        <v>154</v>
+      </c>
+      <c r="F6" s="10">
+        <v>159</v>
+      </c>
+      <c r="G6" s="10">
+        <v>176</v>
+      </c>
+      <c r="H6" s="10">
+        <v>202</v>
+      </c>
+      <c r="I6" s="10">
+        <v>220</v>
+      </c>
+      <c r="J6" s="10">
+        <v>258</v>
+      </c>
+      <c r="K6" s="10">
+        <v>276</v>
+      </c>
+      <c r="L6" s="10">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="10">
+        <v>175</v>
+      </c>
+      <c r="C7" s="10">
+        <v>176</v>
+      </c>
+      <c r="D7" s="10">
+        <v>180</v>
+      </c>
+      <c r="E7" s="10">
+        <v>199</v>
+      </c>
+      <c r="F7" s="10">
+        <v>245</v>
+      </c>
+      <c r="G7" s="10">
+        <v>261</v>
+      </c>
+      <c r="H7" s="10">
+        <v>272</v>
+      </c>
+      <c r="I7" s="10">
+        <v>286</v>
+      </c>
+      <c r="J7" s="10">
+        <v>279</v>
+      </c>
+      <c r="K7" s="10">
+        <v>304</v>
+      </c>
+      <c r="L7" s="10">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="10">
+        <v>89</v>
+      </c>
+      <c r="C8" s="10">
+        <v>92</v>
+      </c>
+      <c r="D8" s="10">
+        <v>88</v>
+      </c>
+      <c r="E8" s="10">
+        <v>116</v>
+      </c>
+      <c r="F8" s="10">
+        <v>203</v>
+      </c>
+      <c r="G8" s="10">
+        <v>189</v>
+      </c>
+      <c r="H8" s="10">
+        <v>193</v>
+      </c>
+      <c r="I8" s="10">
+        <v>203</v>
+      </c>
+      <c r="J8" s="10">
+        <v>244</v>
+      </c>
+      <c r="K8" s="10">
+        <v>266</v>
+      </c>
+      <c r="L8" s="10">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B0B285-2017-4174-A96C-88E1B3B82AD1}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>5</v>
+      </c>
+      <c r="B2" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>12</v>
+      </c>
+      <c r="B3" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>9</v>
+      </c>
+      <c r="B4" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>15</v>
+      </c>
+      <c r="B5" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>6</v>
+      </c>
+      <c r="B6" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>7</v>
+      </c>
+      <c r="B7" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>6</v>
+      </c>
+      <c r="B8" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F000942-8A84-46B3-8480-9C5561E0F5A1}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="10">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10">
+        <v>300</v>
+      </c>
+      <c r="D2" s="10">
+        <v>6</v>
+      </c>
+      <c r="E2" s="10">
+        <v>280</v>
+      </c>
+      <c r="F2" s="10">
+        <v>6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="10">
+        <v>32</v>
+      </c>
+      <c r="C3" s="10">
+        <v>150</v>
+      </c>
+      <c r="D3" s="10">
+        <v>36</v>
+      </c>
+      <c r="E3" s="10">
+        <v>120</v>
+      </c>
+      <c r="F3" s="10">
+        <v>38</v>
+      </c>
+      <c r="G3" s="10">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="10">
+        <v>6</v>
+      </c>
+      <c r="C4" s="10">
+        <v>120</v>
+      </c>
+      <c r="D4" s="10">
+        <v>7</v>
+      </c>
+      <c r="E4" s="10">
+        <v>130</v>
+      </c>
+      <c r="F4" s="10">
+        <v>8</v>
+      </c>
+      <c r="G4" s="10">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="10">
+        <v>27</v>
+      </c>
+      <c r="C5" s="10">
+        <v>50</v>
+      </c>
+      <c r="D5" s="10">
+        <v>30</v>
+      </c>
+      <c r="E5" s="10">
+        <v>55</v>
+      </c>
+      <c r="F5" s="10">
+        <v>40</v>
+      </c>
+      <c r="G5" s="10">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Ejemplos_Excel/Datos_Ejemplos.xlsx
+++ b/Ejemplos_Excel/Datos_Ejemplos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Semestre 1-2026\Trabajo Dirigido\Proyecto\Proyecto_SHC170\Ejemplos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC398FAD-0C45-4E61-B2E5-B693ABD3FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07253135-AF36-4B9C-A259-4E30D9FDD038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11130" yWindow="2370" windowWidth="14730" windowHeight="11295" firstSheet="11" activeTab="13" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="11" activeTab="12" xr2:uid="{F673EB76-743D-4B0D-96C3-C32891F51760}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos_Ej1" sheetId="2" r:id="rId1"/>
@@ -25,8 +25,9 @@
     <sheet name="Ejemplo 5.8 (Regresion)" sheetId="11" r:id="rId10"/>
     <sheet name="Ejemplo 6.1 (N.Indices)" sheetId="14" r:id="rId11"/>
     <sheet name="Ejemplo 6.2 (N.Indices)" sheetId="15" r:id="rId12"/>
-    <sheet name="Ejemplo 5.7 (Regresion Cuad.)" sheetId="16" r:id="rId13"/>
-    <sheet name="Ejemplo 6.9 (N. Indice)" sheetId="17" r:id="rId14"/>
+    <sheet name="Hoja1" sheetId="18" r:id="rId13"/>
+    <sheet name="Ejemplo 5.7 (Regresion Cuad.)" sheetId="16" r:id="rId14"/>
+    <sheet name="Ejemplo 6.9 (N. Indice)" sheetId="17" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1709,6 +1710,98 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BD8D67-1733-43C7-B549-946A534FFF6F}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <v>5</v>
+      </c>
+      <c r="C1">
+        <v>6</v>
+      </c>
+      <c r="D1">
+        <v>10</v>
+      </c>
+      <c r="E1">
+        <v>85</v>
+      </c>
+      <c r="F1">
+        <v>10</v>
+      </c>
+      <c r="G1">
+        <v>58</v>
+      </c>
+      <c r="H1">
+        <v>45</v>
+      </c>
+      <c r="I1">
+        <v>5</v>
+      </c>
+      <c r="J1">
+        <v>6</v>
+      </c>
+      <c r="K1">
+        <v>7</v>
+      </c>
+      <c r="L1">
+        <v>8</v>
+      </c>
+      <c r="M1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B0B285-2017-4174-A96C-88E1B3B82AD1}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1809,7 +1902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F000942-8A84-46B3-8480-9C5561E0F5A1}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
